--- a/data/3_квартал_2026.xlsx
+++ b/data/3_квартал_2026.xlsx
@@ -11225,7 +11225,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M130" s="4" t="n"/>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M131" s="4" t="n"/>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M132" s="4" t="n"/>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M133" s="4" t="n"/>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M134" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M135" s="4" t="n"/>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M136" s="4" t="n"/>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M137" s="4" t="n"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M141" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M142" s="4" t="n"/>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M143" s="4" t="n"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M144" s="4" t="n"/>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M145" s="4" t="n"/>
@@ -12281,7 +12281,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M146" s="4" t="n"/>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M147" s="4" t="n"/>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УПН Корпус №13</t>
         </is>
       </c>
       <c r="M148" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M149" s="4" t="n"/>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M150" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M151" s="4" t="n"/>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M152" s="4" t="n"/>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M153" s="4" t="n"/>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M154" s="4" t="n"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M155" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M156" s="4" t="n"/>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M157" s="4" t="n"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M159" s="4" t="n"/>
@@ -13205,7 +13205,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M160" s="4" t="n"/>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M164" s="4" t="n"/>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M171" s="4" t="n"/>
@@ -14063,7 +14063,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M173" s="4" t="n"/>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M174" s="4" t="n"/>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M175" s="4" t="n"/>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M176" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M177" s="4" t="n"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M178" s="4" t="n"/>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M179" s="4" t="n"/>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M180" s="4" t="n"/>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M181" s="4" t="n"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M182" s="4" t="n"/>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M183" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M184" s="4" t="n"/>
@@ -14855,7 +14855,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M185" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M186" s="4" t="n"/>
@@ -14987,7 +14987,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M187" s="4" t="n"/>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M188" s="4" t="n"/>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M189" s="4" t="n"/>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M190" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M193" s="4" t="n"/>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M194" s="4" t="n"/>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M195" s="4" t="n"/>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M196" s="4" t="n"/>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M198" s="4" t="n"/>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M199" s="4" t="n"/>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>Корпус №13</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M200" s="4" t="n"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M201" s="4" t="n"/>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M202" s="4" t="n"/>
@@ -16043,7 +16043,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>Корпус №11</t>
+          <t>УМИ Корпус №11</t>
         </is>
       </c>
       <c r="M203" s="4" t="n"/>
@@ -16371,7 +16371,11 @@
           <t>Устранено</t>
         </is>
       </c>
-      <c r="L208" s="4" t="n"/>
+      <c r="L208" s="4" t="inlineStr">
+        <is>
+          <t>УМИ Корпус №11</t>
+        </is>
+      </c>
       <c r="M208" s="4" t="n"/>
       <c r="N208" s="6" t="inlineStr">
         <is>
@@ -16433,7 +16437,11 @@
           <t>Устранено</t>
         </is>
       </c>
-      <c r="L209" s="4" t="n"/>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>УМИ Корпус №11</t>
+        </is>
+      </c>
       <c r="M209" s="4" t="n"/>
       <c r="N209" s="6" t="inlineStr">
         <is>
@@ -16495,7 +16503,11 @@
           <t>Устранено</t>
         </is>
       </c>
-      <c r="L210" s="4" t="n"/>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>УМИ Корпус №11</t>
+        </is>
+      </c>
       <c r="M210" s="4" t="n"/>
       <c r="N210" s="6" t="inlineStr">
         <is>
